--- a/testing/Howler_QA_Fixes_Applied.xlsx
+++ b/testing/Howler_QA_Fixes_Applied.xlsx
@@ -433,13 +433,14 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F17"/>
   <cols>
     <col min="1" max="1" width="46.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,7 +450,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Fixes applied 2026-07-25, working the prioritized failed-test list (29 cases, production audit) top to bottom</v>
+        <v>Fixes applied 2026-07-25, working the prioritized failed-test list (29 cases, production audit) top to bottom. Regression-tested against a local server running the patched code on 2026-07-26.</v>
       </c>
     </row>
     <row r="4">
@@ -473,9 +474,12 @@
         <v>Fixed</v>
       </c>
       <c r="D7" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="E7" t="str">
         <v>Deferred</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>Sheet</v>
       </c>
     </row>
@@ -487,12 +491,15 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <v>1. Function</v>
       </c>
     </row>
@@ -509,7 +516,10 @@
       <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="str">
         <v>2. Security</v>
       </c>
     </row>
@@ -524,9 +534,12 @@
         <v>5</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>3. Accessibility &amp; UI</v>
       </c>
     </row>
@@ -538,12 +551,15 @@
         <v>29</v>
       </c>
       <c r="C11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
         <v/>
       </c>
     </row>
@@ -559,17 +575,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>- Deferred rows (RT-04, A11Y-03) were left alone deliberately, not skipped by oversight — see their 'Fix Applied' cell for why.</v>
+        <v>- Regression-tested 2026-07-26 against a local server running this exact code, using a real authenticated session: 15/17 targeted checks passed outright.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>- 'Related / Notes' still flags shared root causes; several rows were closed together by one change (see 'Files Changed').</v>
+        <v>- 2 checks (PERF-04, NEW-02) surfaced a real gap during regression and are now marked 'Partially Fixed', not 'Fixed' — both need DB/Storage-level access (service-role key or dashboard) this session does not have. See their 'Fix Applied' cell for specifics.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>- Deferred rows (RT-04, A11Y-03) were left alone deliberately, not skipped by oversight — see their 'Fix Applied' cell for why.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1002,10 +1023,10 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>Fixed</v>
+        <v>Partially Fixed</v>
       </c>
       <c r="J12" t="str">
-        <v>Added a server-side dedupe check before insert: if the same user posted identical content+category in the last 5 seconds, the existing row is returned instead of creating a duplicate. Closes the gap where two concurrent identical requests both previously succeeded.</v>
+        <v>Added a server-side dedupe check before insert (same user + identical content/category within 5 seconds returns the existing row instead of inserting a new one). REGRESSION-TESTED 2026-07-26: this narrows the bug substantially but does not fully close it — re-running the original scenario (two truly concurrent requests via Promise.all) still produced 2 rows, because a SELECT-then-INSERT check has an inherent race under true concurrency. Fully closing it needs a DB-level unique constraint or a serialized/advisory-lock RPC, which requires schema/migration access this session does not have (only the anon publishable key is available, no service-role key or DB connection string).</v>
       </c>
       <c r="K12" t="str">
         <v>src/app/api/posts/route.js</v>
@@ -1177,10 +1198,10 @@
         <v>Cost accumulation now; also means a "delete because the image was wrong" action doesn't actually remove the image.</v>
       </c>
       <c r="I17" t="str">
-        <v>Fixed</v>
+        <v>Partially Fixed</v>
       </c>
       <c r="J17" t="str">
-        <v>delete_post now looks up the post's image_url before deleting the row, then calls supabase.storage.from('posts').remove() on the corresponding Storage path afterward.</v>
+        <v>delete_post now looks up the post's image_url before deleting the row and calls supabase.storage.from('posts').remove() on the corresponding Storage path. REGRESSION-TESTED 2026-07-26: the code path is correct (verified the exact right storage path is computed) but remove() silently returns 0 files removed with no error — the same silent-no-op shape as a filtered DB delete matching zero rows. This strongly points to the 'posts' Storage bucket having no DELETE RLS policy for object owners, which can only be added via the Supabase dashboard/service-role access this session does not have. Added a console.error when remove() reports 0 files removed, so this failure is now visible in server logs instead of silent.</v>
       </c>
       <c r="K17" t="str">
         <v>src/app/api/delete_post/route.js</v>
